--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,9 +781,235 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137017875</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>765687</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7097990</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137017875</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137017876</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Melsbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>766019</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7097910</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137017876</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -786,7 +786,7 @@
         <v>137017875</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80865235</v>
+        <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>83173</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rävatjärnberget, Vb</t>
+          <t>Rävatjärn, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>765739</v>
+        <v>765971</v>
       </c>
       <c r="R2" t="n">
-        <v>7097707</v>
+        <v>7097832</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,69 +769,68 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Alva Danielsson, Alexander Ahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80865235</t>
+          <t>https://artportalen.se/Sighting/137063524</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137017875</v>
+        <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granbäck, Vb</t>
+          <t>Rävatjärn, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765687</v>
+        <v>765954</v>
       </c>
       <c r="R3" t="n">
-        <v>7097990</v>
+        <v>7097900</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -848,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,22 +892,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Alva Danielsson, Alexander Ahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137017875</t>
+          <t>https://artportalen.se/Sighting/137063529</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137017876</v>
+        <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>92549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Melsbäck, Vb</t>
+          <t>Rävatjärn, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766019</v>
+        <v>765953</v>
       </c>
       <c r="R4" t="n">
-        <v>7097910</v>
+        <v>7097901</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,13 +1004,1358 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Alva Danielsson, Alexander Ahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137063530</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>80865235</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rävatjärnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>765739</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7097707</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80865235</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137058395</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83349</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rävtjärnen, Ersboda, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>765957</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7097892</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137058395</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137063522</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92080</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>765985</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7097857</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063522</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137063538</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92080</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>765798</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7097643</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063538</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137017875</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>765687</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7097990</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137017875</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137063539</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>765679</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7097705</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063539</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137063541</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>765631</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7097818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063541</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137063543</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>765613</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7097894</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063543</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137063542</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>765612</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7097900</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063542</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137069965</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ersmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>765725</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7097760</v>
+      </c>
+      <c r="S14" t="n">
+        <v>99</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137069965</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137017876</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Melsbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>766019</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7097910</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137017876</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137063540</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rävatjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>765670</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7097702</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Alexander Ahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137063540</t>
         </is>
       </c>
     </row>
@@ -1010,6 +2364,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137063542</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>137069965</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>137017876</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>137063540</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137063542</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>137069965</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>137017876</v>
       </c>
       <c r="B15" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>137063540</v>
       </c>
       <c r="B16" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -1932,11 +1932,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rävatjärn, Vb</t>
@@ -2273,11 +2269,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävatjärn, Vb</t>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137063542</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>137069965</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137017876</v>
       </c>
       <c r="B15" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>137063540</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137063542</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>137069965</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137017876</v>
       </c>
       <c r="B15" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>137063540</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137063542</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>137069965</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137017876</v>
       </c>
       <c r="B15" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>137063540</v>
       </c>
       <c r="B16" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40442-2026 artfynd.xlsx
+++ b/artfynd/A 40442-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137063524</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137063529</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137063530</v>
       </c>
       <c r="B4" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137058395</v>
       </c>
       <c r="B6" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137063522</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137063538</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>137017875</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137063539</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137063541</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137063543</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137063542</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>137069965</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137017876</v>
       </c>
       <c r="B15" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>137063540</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
